--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536126_LIGAREGULARA_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536126_LIGAREGULARA_PROCESSED.xlsx
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. GUTIERREZ O´CALLAGHAN</t>
+          <t>E. GUTIERREZ O CALLAGHAN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
